--- a/untranslated/downloads/data-excel/11.6.1.2.xlsx
+++ b/untranslated/downloads/data-excel/11.6.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E00E2F3-B745-411E-98DC-DE2EBE7448A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,15 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
-    <t>11.6.1.1a Избавление от твердых бытовых отходов домашними хозяйствами по видам (мусоропровод; сбор грузовиком, контейнером; сброс в мусорные кучи; сжигание; закапывание)</t>
-  </si>
-  <si>
-    <t>11.6.1.1а Түрлөрү боюнча (таштанды түтүгү, жүк ташуучу машина, контейнер менен жыйноо, таштанды үймөктөрүнө таштоо, өрттөө, көмүү) үй чарбаларынын турмуш-катуу тиричилик калдыктарын тазалоо</t>
-  </si>
-  <si>
-    <t>11.6.1.1a Disposal of municipal solid waste by households by type (garbage chute; collection by truck, container; dumping in garbage piles; incineration; landfill)</t>
-  </si>
-  <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
   <si>
@@ -86,12 +78,21 @@
   </si>
   <si>
     <t>(in percent)</t>
+  </si>
+  <si>
+    <t>11.6.1.2 Disposal of municipal solid waste by households by type (garbage chute; collection by truck, container; dumping in garbage piles; incineration; landfill)</t>
+  </si>
+  <si>
+    <t>11.6.1.2 Избавление от твердых бытовых отходов домашними хозяйствами по видам (мусоропровод; сбор грузовиком, контейнером; сброс в мусорные кучи; сжигание; закапывание)</t>
+  </si>
+  <si>
+    <t>11.6.1.2 Түрлөрү боюнча (таштанды түтүгү, жүк ташуучу машина, контейнер менен жыйноо, таштанды үймөктөрүнө таштоо, өрттөө, көмүү) үй чарбаларынын турмуш-катуу тиричилик калдыктарын тазалоо</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -178,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -204,23 +205,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,7 +214,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 5" xfId="1"/>
+    <cellStyle name="Обычный 5" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -244,9 +230,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -284,9 +270,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -321,7 +307,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -356,7 +342,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,8 +515,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="39.42578125" style="1" customWidth="1"/>
@@ -538,29 +524,29 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -575,16 +561,17 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" s="5">
         <v>2013</v>
@@ -607,28 +594,31 @@
       <c r="J4" s="5">
         <v>2019</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="5">
         <v>2020</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="5">
         <v>2021</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="5">
         <v>2022</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="5">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="5">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6">
         <v>0.3</v>
@@ -651,28 +641,31 @@
       <c r="J5" s="6">
         <v>0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="6">
         <v>0</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="6">
         <v>0</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="6">
         <v>0</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6">
         <v>26.9</v>
@@ -695,28 +688,31 @@
       <c r="J6" s="1">
         <v>46.9</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="9">
         <v>48.2</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="9">
         <v>58.405380200320216</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="9">
         <v>48.6</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="9">
         <v>48.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="9">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6">
         <v>21.6</v>
@@ -739,28 +735,31 @@
       <c r="J7" s="1">
         <v>20.2</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="1">
         <v>19.3</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="8">
         <v>11.673077354810609</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="1">
         <v>20.2</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="1">
         <v>23.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="8">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" s="6">
         <v>33</v>
@@ -783,28 +782,31 @@
       <c r="J8" s="8">
         <v>24</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="8">
         <v>24.2</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="8">
         <v>22.564920591204277</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="8">
         <v>22.9</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="8">
         <v>19.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O8" s="8">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D9" s="7">
         <v>18.2</v>
@@ -827,20 +829,23 @@
       <c r="J9" s="7">
         <v>8.9</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="7">
         <v>7.3566218536648895</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="7">
         <v>9.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="7">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
